--- a/FedMilLiPst2BT.xlsx
+++ b/FedMilLiPst2BT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\FedGMil\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC05165A-7548-4CE9-866E-4197F0ECCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F696D8-ECC6-4727-8EEE-9F08CE156578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E40483B6-39FD-41F9-8114-0C357F62372C}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>COMMAND_TIER</t>
   </si>
   <si>
-    <t>FEDERAL_AGENCY_BRANCH</t>
-  </si>
-  <si>
     <t>REQUIRED_REPLENISHMENT_UNITS</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>US Army</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -831,6 +831,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -838,15 +847,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -866,11 +866,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48318710-09A8-4439-85E5-B16A20C9A8C2}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48318710-09A8-4439-85E5-B16A20C9A8C2}" name="Table1" displayName="Table1" ref="A1:E11" totalsRowShown="0" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E11" xr:uid="{48318710-09A8-4439-85E5-B16A20C9A8C2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C3848891-ADE6-4DC2-A28D-746072C13C5A}" name="COMMAND_TIER" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{EC7FC365-132B-44B2-8C6E-18B87A8078BB}" name="FEDERAL_AGENCY_BRANCH" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{EC7FC365-132B-44B2-8C6E-18B87A8078BB}" name="Agency" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{40B16F05-9FA7-42E6-A0CF-30698EC9BEF6}" name="REQUIRED_REPLENISHMENT_UNITS" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{37E146A0-EA76-4986-AEB2-707158026364}" name="AVERAGE_UNIT_COST_MSRP" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{DC2D7271-E8F4-4406-8A39-0557642961F8}" name="ESTIMATED_REMEDIATION_BUDGET" dataDxfId="0"/>
@@ -1211,24 +1211,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="3">
         <v>10547</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3">
         <v>9863</v>
@@ -1259,10 +1259,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="3">
         <v>9179</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3">
         <v>8495</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
         <v>7811</v>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="C7" s="3">
         <v>7120</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>6241</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>5899</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>5215</v>
@@ -1378,10 +1378,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="12">
         <v>2489</v>
